--- a/_other/WSTREE.xlsx
+++ b/_other/WSTREE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DDBBAFF-B007-436A-8BC0-327C04E4C4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7C40A2-E7A2-4163-B24C-36D130AF5002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="240">
   <si>
     <t>PTA2_BDDC_FIX</t>
   </si>
@@ -770,6 +770,9 @@
   </si>
   <si>
     <t>STARL1_HELPGOD</t>
+  </si>
+  <si>
+    <t>PTA30_</t>
   </si>
 </sst>
 </file>
@@ -2907,6 +2910,9 @@
       <c r="A90">
         <v>89</v>
       </c>
+      <c r="B90" s="2" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">

--- a/_other/WSTREE.xlsx
+++ b/_other/WSTREE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7C40A2-E7A2-4163-B24C-36D130AF5002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5371B676-2B71-4FA0-98E8-16F505239426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="241">
   <si>
     <t>PTA2_BDDC_FIX</t>
   </si>
@@ -772,7 +772,10 @@
     <t>STARL1_HELPGOD</t>
   </si>
   <si>
-    <t>PTA30_</t>
+    <t>PTA30_LILI</t>
+  </si>
+  <si>
+    <t>PTA30_RAYNOR</t>
   </si>
 </sst>
 </file>
@@ -2910,13 +2913,16 @@
       <c r="A90">
         <v>89</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B90" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
